--- a/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134739</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:39+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152100</t>
+    <t>20251028115832</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:00+01:00</t>
+    <t>2025-10-28T11:58:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,19 +96,19 @@
     <t>24028007</t>
   </si>
   <si>
-    <t>droit</t>
+    <t>côté droit</t>
   </si>
   <si>
     <t>7771000</t>
   </si>
   <si>
-    <t>gauche</t>
+    <t>côté gauche</t>
   </si>
   <si>
     <t>51440002</t>
   </si>
   <si>
-    <t>bilatéral</t>
+    <t>bilatéral(e)</t>
   </si>
   <si>
     <t>66459002</t>
@@ -222,13 +222,13 @@
     <t>60583000</t>
   </si>
   <si>
-    <t>postaxial</t>
+    <t>postaxial(e)</t>
   </si>
   <si>
     <t>32400000</t>
   </si>
   <si>
-    <t>préaxial</t>
+    <t>préaxial(e)</t>
   </si>
   <si>
     <t>43674008</t>
@@ -294,7 +294,7 @@
     <t>30730003</t>
   </si>
   <si>
-    <t>sagital(le)</t>
+    <t>sagittal(e)</t>
   </si>
   <si>
     <t>24422004</t>
@@ -366,7 +366,7 @@
     <t>112233002</t>
   </si>
   <si>
-    <t>marginal</t>
+    <t>marginal(e)</t>
   </si>
   <si>
     <t/>

--- a/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251028115832</t>
+    <t>20251216141838</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T11:58:32+01:00</t>
+    <t>2025-12-16T14:18:38+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142103</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142103</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:03+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,6 +367,48 @@
   </si>
   <si>
     <t>marginal(e)</t>
+  </si>
+  <si>
+    <t>7970006</t>
+  </si>
+  <si>
+    <t>allogreffe</t>
+  </si>
+  <si>
+    <t>15879007</t>
+  </si>
+  <si>
+    <t>autogreffe</t>
+  </si>
+  <si>
+    <t>67650000</t>
+  </si>
+  <si>
+    <t>hétérogreffe</t>
+  </si>
+  <si>
+    <t>16404004</t>
+  </si>
+  <si>
+    <t>induit(e)</t>
+  </si>
+  <si>
+    <t>67194007</t>
+  </si>
+  <si>
+    <t>isogreffe</t>
+  </si>
+  <si>
+    <t>18769003</t>
+  </si>
+  <si>
+    <t>juxtaposé(e)</t>
+  </si>
+  <si>
+    <t>5054005</t>
+  </si>
+  <si>
+    <t>spontané(e)</t>
   </si>
   <si>
     <t/>
@@ -631,7 +673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1019,15 +1061,71 @@
         <v>118</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-modificateur-topographique-cisis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="137">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150249</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:49+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -409,6 +409,12 @@
   </si>
   <si>
     <t>spontané(e)</t>
+  </si>
+  <si>
+    <t>255562008</t>
+  </si>
+  <si>
+    <t>milieu</t>
   </si>
   <si>
     <t/>
@@ -673,7 +679,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1117,15 +1123,23 @@
         <v>132</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>134</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
